--- a/output/pdf_financials_xlsx/GCN.xlsx
+++ b/output/pdf_financials_xlsx/GCN.xlsx
@@ -5981,40 +5981,40 @@
         <v>2.285859</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.406214</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.496939</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.496939</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.509112</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.801507</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.801507</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.981748</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.273309</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.118625</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.953602</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.989655</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.80184</v>
       </c>
     </row>
     <row r="93">
@@ -7459,16 +7459,16 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.37819</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.21946</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.227654</v>
+        <v>0.130949</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000375</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0.025</v>
@@ -9652,7 +9652,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -9919,7 +9923,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10604,7 +10612,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10804,7 +10816,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11315,7 +11331,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -11824,7 +11844,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -13260,7 +13284,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -28123,7 +28151,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -31048,7 +31080,11 @@
           <t>Exploration and evaluation of assets expenditures</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -43989,7 +44025,7 @@
         <v>-1.132871</v>
       </c>
       <c r="O356" s="5" t="n">
-        <v>0.206802</v>
+        <v>-0.206802</v>
       </c>
       <c r="P356" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GCN.xlsx
+++ b/output/pdf_financials_xlsx/GCN.xlsx
@@ -933,10 +933,10 @@
         <v>0.48699</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.605473</v>
+        <v>0.905881</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.087089</v>
+        <v>0.783447</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.062746</v>
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000676</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000463</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>-0.904856</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.339651</v>
+        <v>-0.340327</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.305839</v>
+        <v>-0.306302</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.112152</v>
@@ -2120,10 +2120,10 @@
         <v>-0.895657</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.337226</v>
+        <v>-0.337902</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.305839</v>
+        <v>-0.306302</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.112152</v>
@@ -2412,55 +2412,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.005592</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.005592</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.012765</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.010399</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.052182</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.062309</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.042854</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.662266</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.013673</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.005255</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.879775</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.429789</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.096362</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.022663</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.016556</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.223535</v>
       </c>
     </row>
     <row r="35">
@@ -2528,55 +2528,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.005592</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.005592</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.012765</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.010399</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.052182</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.062309</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.042854</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.662266</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.013673</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.005255</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.879775</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.44</v>
+        <v>0.869789</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.11</v>
+        <v>0.206362</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.04125</v>
+        <v>0.063913</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.07425</v>
+        <v>0.090806</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.0039</v>
+        <v>0.227435</v>
       </c>
     </row>
     <row r="37">
@@ -3224,55 +3224,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.013454</v>
+        <v>0.008354</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.017051</v>
+        <v>0.011459</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.005592</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.014998</v>
+        <v>0.002233</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.055164</v>
+        <v>0.002982</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.062309</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.042854</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.662266</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.017508</v>
+        <v>0.003835</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.005255</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.879775</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.435531</v>
+        <v>0.005742</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.096362</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.022663</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.016556</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.223535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -16875,7 +16875,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
@@ -42062,7 +42062,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -48908,7 +48908,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -50643,7 +50643,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">

--- a/output/pdf_financials_xlsx/GCN.xlsx
+++ b/output/pdf_financials_xlsx/GCN.xlsx
@@ -750,7 +750,7 @@
         <v>0.168489</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.063329</v>
+        <v>0.134787</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.36447</v>
@@ -924,7 +924,7 @@
         <v>0.177294</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.06963900000000001</v>
+        <v>0.141097</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.372739</v>
@@ -17176,7 +17176,11 @@
           <t>Equipment – Note 3</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -17275,7 +17279,11 @@
           <t>Mineral properties – Note 4</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -17477,7 +17485,11 @@
           <t>Due to related parties – Note 7</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -17677,7 +17689,11 @@
           <t>Share capital – Note 5</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -17776,7 +17792,11 @@
           <t>Contributed surplus – Note 5</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -55824,7 +55844,11 @@
           <t>Management fees – Note 7</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
@@ -56026,7 +56050,11 @@
           <t>Professional fees – Note 7</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
           <t>-</t>
@@ -56224,7 +56252,11 @@
           <t>Rent – Note 7</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
@@ -56323,7 +56355,11 @@
           <t>Shareholder communication – Note 7</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GCN.xlsx
+++ b/output/pdf_financials_xlsx/GCN.xlsx
@@ -7120,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.033606</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -28070,7 +28070,11 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GCN.xlsx
+++ b/output/pdf_financials_xlsx/GCN.xlsx
@@ -1284,7 +1284,7 @@
         <v>-0.904856</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.339651</v>
+        <v>-0.333368</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-0.305839</v>
@@ -1342,7 +1342,7 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.006283</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1360,7 +1360,7 @@
         <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.005272</v>
+        <v>-0.005272</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0</v>
@@ -2004,7 +2004,7 @@
         <v>-0.904856</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.340327</v>
+        <v>-0.334044</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.306302</v>
@@ -2120,7 +2120,7 @@
         <v>-0.895657</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.337902</v>
+        <v>-0.331619</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.306302</v>
@@ -2270,7 +2270,7 @@
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.884703990784958</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -4250,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.039988</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.312556</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -4424,13 +4424,13 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0145</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.02389</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -4442,25 +4442,25 @@
         <v>0</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.036079</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.040144</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.040144</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.047645</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.047145</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.038632</v>
       </c>
     </row>
     <row r="68">
@@ -6473,7 +6473,7 @@
         <v>-0.007565</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.019456</v>
+        <v>-0.032487</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0.003912</v>
@@ -6763,7 +6763,7 @@
         <v>-0.002914851</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.455391</v>
+        <v>-0.468422</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.155045</v>
@@ -7120,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0.033606</v>
+        <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.057994</v>
       </c>
     </row>
     <row r="116">
@@ -19837,7 +19837,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -20041,7 +20045,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -23816,7 +23824,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -26426,7 +26438,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -28070,11 +28086,7 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -30714,7 +30726,11 @@
           <t>Proceeds from share issuances 6</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -31716,7 +31732,11 @@
           <t>Write-off of GST recoverable</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -32439,7 +32459,11 @@
           <t>Write-off of GST recoverable</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -42589,7 +42613,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -49033,7 +49061,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
